--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ).xlsx
@@ -587,7 +587,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -767,6 +767,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -776,7 +779,7 @@
               <c:f>'model2(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -955,6 +958,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -998,7 +1004,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1178,6 +1184,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1187,7 +1196,7 @@
               <c:f>'model2(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1367,6 +1376,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1978849.1612350328</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2022104.2217609019</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1409,7 +1421,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1589,6 +1601,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1598,7 +1613,7 @@
               <c:f>'model2(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1778,6 +1793,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>820356.13175280904</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>863611.19227867806</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1799,11 +1817,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="442374016"/>
-        <c:axId val="448737280"/>
+        <c:axId val="492285312"/>
+        <c:axId val="494511232"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="442374016"/>
+        <c:axId val="492285312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1846,14 +1864,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="448737280"/>
+        <c:crossAx val="494511232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="448737280"/>
+        <c:axId val="494511232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1904,7 +1922,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="442374016"/>
+        <c:crossAx val="492285312"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2065,7 +2083,7 @@
               <c:f>'model2(1)&amp;KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2245,6 +2263,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-36057.366675283578</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-60139.263576626639</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2264,8 +2285,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="442312192"/>
-        <c:axId val="442310656"/>
+        <c:axId val="502472064"/>
+        <c:axId val="502470528"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2290,7 +2311,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2470,6 +2491,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2479,7 +2503,7 @@
               <c:f>'model2(1)&amp;KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2659,6 +2683,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2680,11 +2707,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="442307328"/>
-        <c:axId val="442308864"/>
+        <c:axId val="502323840"/>
+        <c:axId val="502468992"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="442307328"/>
+        <c:axId val="502323840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2727,14 +2754,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="442308864"/>
+        <c:crossAx val="502468992"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="442308864"/>
+        <c:axId val="502468992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2785,12 +2812,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="442307328"/>
+        <c:crossAx val="502323840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="442310656"/>
+        <c:axId val="502470528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2827,12 +2854,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="442312192"/>
+        <c:crossAx val="502472064"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="442312192"/>
+        <c:axId val="502472064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2841,7 +2868,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="442310656"/>
+        <c:crossAx val="502470528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2991,7 +3018,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3171,6 +3198,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3180,7 +3210,7 @@
               <c:f>'model2(2)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3359,6 +3389,9 @@
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>8275639.9932962749</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
               </c:numCache>
@@ -3402,7 +3435,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3582,6 +3615,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3591,7 +3627,7 @@
               <c:f>'model2(2)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3771,6 +3807,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>15803331.182775768</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>16174234.157067223</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3813,7 +3852,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3993,6 +4032,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4002,7 +4044,7 @@
               <c:f>'model2(2)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4182,6 +4224,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>7527691.1894794926</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>7898594.1637709476</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4203,11 +4248,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="442327808"/>
-        <c:axId val="442329344"/>
+        <c:axId val="502508160"/>
+        <c:axId val="502522240"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="442327808"/>
+        <c:axId val="502508160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4250,14 +4295,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="442329344"/>
+        <c:crossAx val="502522240"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="442329344"/>
+        <c:axId val="502522240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4308,7 +4353,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="442327808"/>
+        <c:crossAx val="502508160"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4469,7 +4514,7 @@
               <c:f>'model2(2)vol'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4649,6 +4694,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-228232.84251096987</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-703792.54386857653</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4668,8 +4716,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="442353536"/>
-        <c:axId val="442352000"/>
+        <c:axId val="503087104"/>
+        <c:axId val="503081216"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4694,7 +4742,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4874,6 +4922,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4883,7 +4934,7 @@
               <c:f>'model2(2)vol'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5063,6 +5114,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5084,11 +5138,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="442344576"/>
-        <c:axId val="442346112"/>
+        <c:axId val="503069696"/>
+        <c:axId val="503079680"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="442344576"/>
+        <c:axId val="503069696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5131,14 +5185,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="442346112"/>
+        <c:crossAx val="503079680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="442346112"/>
+        <c:axId val="503079680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5189,12 +5243,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="442344576"/>
+        <c:crossAx val="503069696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="442352000"/>
+        <c:axId val="503081216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5231,12 +5285,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="442353536"/>
+        <c:crossAx val="503087104"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="442353536"/>
+        <c:axId val="503087104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5245,7 +5299,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="442352000"/>
+        <c:crossAx val="503081216"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5395,7 +5449,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5575,6 +5629,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5584,7 +5641,7 @@
               <c:f>'model2(2)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5763,6 +5820,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -5806,7 +5866,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5986,6 +6046,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5995,7 +6058,7 @@
               <c:f>'model2(2)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6175,6 +6238,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>16470742.053078819</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>16842108.331714839</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6217,7 +6283,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6397,6 +6463,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6406,7 +6475,7 @@
               <c:f>'model2(2)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6586,6 +6655,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>7109407.2353513949</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>7480773.5139874145</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6607,11 +6679,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="452650112"/>
-        <c:axId val="452651648"/>
+        <c:axId val="505568256"/>
+        <c:axId val="505582336"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="452650112"/>
+        <c:axId val="505568256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6654,14 +6726,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="452651648"/>
+        <c:crossAx val="505582336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="452651648"/>
+        <c:axId val="505582336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6712,7 +6784,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="452650112"/>
+        <c:crossAx val="505568256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6873,7 +6945,7 @@
               <c:f>'model2(2)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7053,6 +7125,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-329147.77001413936</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-915628.10722505616</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7072,8 +7147,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="453163264"/>
-        <c:axId val="453161728"/>
+        <c:axId val="505631104"/>
+        <c:axId val="505625216"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7098,7 +7173,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7278,6 +7353,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7287,7 +7365,7 @@
               <c:f>'model2(2)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7467,6 +7545,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7488,11 +7569,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="453150208"/>
-        <c:axId val="453151744"/>
+        <c:axId val="505617792"/>
+        <c:axId val="505623680"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="453150208"/>
+        <c:axId val="505617792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7535,14 +7616,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="453151744"/>
+        <c:crossAx val="505623680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="453151744"/>
+        <c:axId val="505623680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7593,12 +7674,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="453150208"/>
+        <c:crossAx val="505617792"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="453161728"/>
+        <c:axId val="505625216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7635,12 +7716,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="453163264"/>
+        <c:crossAx val="505631104"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="453163264"/>
+        <c:axId val="505631104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7649,7 +7730,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="453161728"/>
+        <c:crossAx val="505625216"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7781,7 +7862,7 @@
               <c:f>'model2(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7961,6 +8042,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-36057.366675283578</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-60139.263576626639</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7980,8 +8064,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="537083264"/>
-        <c:axId val="533669760"/>
+        <c:axId val="501887744"/>
+        <c:axId val="501885952"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8006,7 +8090,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8186,6 +8270,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8195,7 +8282,7 @@
               <c:f>'model2(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8375,6 +8462,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8396,11 +8486,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="524069120"/>
-        <c:axId val="533668224"/>
+        <c:axId val="501882880"/>
+        <c:axId val="501884416"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="524069120"/>
+        <c:axId val="501882880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8443,14 +8533,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="533668224"/>
+        <c:crossAx val="501884416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="533668224"/>
+        <c:axId val="501884416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8501,12 +8591,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="524069120"/>
+        <c:crossAx val="501882880"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="533669760"/>
+        <c:axId val="501885952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8543,12 +8633,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="537083264"/>
+        <c:crossAx val="501887744"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="537083264"/>
+        <c:axId val="501887744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8557,7 +8647,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="533669760"/>
+        <c:crossAx val="501885952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8707,7 +8797,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8887,6 +8977,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8896,7 +8989,7 @@
               <c:f>'model2(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9075,6 +9168,9 @@
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>1319891.5920995933</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
               </c:numCache>
@@ -9118,7 +9214,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9298,6 +9394,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9307,7 +9406,7 @@
               <c:f>'model2(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9487,6 +9586,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>2247575.650286919</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2300222.1250249241</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9529,7 +9631,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9709,6 +9811,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9718,7 +9823,7 @@
               <c:f>'model2(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9898,6 +10003,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>927684.05818732572</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>980330.5329253308</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9919,11 +10027,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="542306688"/>
-        <c:axId val="542308224"/>
+        <c:axId val="501915648"/>
+        <c:axId val="501917184"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="542306688"/>
+        <c:axId val="501915648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9966,14 +10074,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="542308224"/>
+        <c:crossAx val="501917184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="542308224"/>
+        <c:axId val="501917184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10024,7 +10132,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="542306688"/>
+        <c:crossAx val="501915648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10206,7 +10314,7 @@
               <c:f>'model2(1)&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10386,6 +10494,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-36057.366675283578</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-60139.263576626639</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10405,8 +10516,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="399474688"/>
-        <c:axId val="399472896"/>
+        <c:axId val="501949952"/>
+        <c:axId val="501948416"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10431,7 +10542,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10611,6 +10722,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10620,7 +10734,7 @@
               <c:f>'model2(1)&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10800,6 +10914,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10821,11 +10938,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="614939648"/>
-        <c:axId val="399471360"/>
+        <c:axId val="501940992"/>
+        <c:axId val="501942528"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="614939648"/>
+        <c:axId val="501940992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10868,14 +10985,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399471360"/>
+        <c:crossAx val="501942528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="399471360"/>
+        <c:axId val="501942528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10926,12 +11043,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="614939648"/>
+        <c:crossAx val="501940992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="399472896"/>
+        <c:axId val="501948416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10968,12 +11085,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399474688"/>
+        <c:crossAx val="501949952"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="399474688"/>
+        <c:axId val="501949952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10982,7 +11099,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="399472896"/>
+        <c:crossAx val="501948416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11132,7 +11249,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11312,6 +11429,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11321,7 +11441,7 @@
               <c:f>'model2(2)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11500,6 +11620,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -11543,7 +11666,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11723,6 +11846,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11732,7 +11858,7 @@
               <c:f>'model2(2)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11912,6 +12038,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>19051655.379257303</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>19503027.168851279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11954,7 +12083,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12134,6 +12263,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12143,7 +12275,7 @@
               <c:f>'model2(2)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12323,6 +12455,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>8163819.6057763249</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>8615191.3953703009</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12344,11 +12479,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="401497088"/>
-        <c:axId val="401507072"/>
+        <c:axId val="502018816"/>
+        <c:axId val="502020352"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="401497088"/>
+        <c:axId val="502018816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12391,14 +12526,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401507072"/>
+        <c:crossAx val="502020352"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="401507072"/>
+        <c:axId val="502020352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12449,7 +12584,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401497088"/>
+        <c:crossAx val="502018816"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12631,7 +12766,7 @@
               <c:f>'model2(2)&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12811,6 +12946,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-329147.77001413936</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-915628.10722505616</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12830,8 +12968,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="401523456"/>
-        <c:axId val="401521664"/>
+        <c:axId val="502081792"/>
+        <c:axId val="502080256"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -12856,7 +12994,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13036,6 +13174,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13045,7 +13186,7 @@
               <c:f>'model2(2)&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -13225,6 +13366,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13246,11 +13390,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="401518592"/>
-        <c:axId val="401520128"/>
+        <c:axId val="502060544"/>
+        <c:axId val="502062080"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="401518592"/>
+        <c:axId val="502060544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13293,14 +13437,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401520128"/>
+        <c:crossAx val="502062080"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="401520128"/>
+        <c:axId val="502062080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13351,12 +13495,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401518592"/>
+        <c:crossAx val="502060544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="401521664"/>
+        <c:axId val="502080256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13393,12 +13537,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401523456"/>
+        <c:crossAx val="502081792"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="401523456"/>
+        <c:axId val="502081792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13407,7 +13551,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="401521664"/>
+        <c:crossAx val="502080256"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13557,7 +13701,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13737,6 +13881,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13746,7 +13893,7 @@
               <c:f>'model2(2)vol&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13925,6 +14072,9 @@
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>1319095.5916679052</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
               </c:numCache>
@@ -13968,7 +14118,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14148,6 +14298,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14157,7 +14310,7 @@
               <c:f>'model2(2)vol&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14337,6 +14490,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>2518827.8975449791</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2579594.8543026936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14379,7 +14535,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14559,6 +14715,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14568,7 +14727,7 @@
               <c:f>'model2(2)vol&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14748,6 +14907,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1199732.3058770739</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1260499.2626347884</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14769,11 +14931,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="426328064"/>
-        <c:axId val="426329600"/>
+        <c:axId val="502105600"/>
+        <c:axId val="502107136"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="426328064"/>
+        <c:axId val="502105600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14816,14 +14978,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426329600"/>
+        <c:crossAx val="502107136"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="426329600"/>
+        <c:axId val="502107136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14874,7 +15036,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426328064"/>
+        <c:crossAx val="502105600"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15035,7 +15197,7 @@
               <c:f>'model2(2)vol&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15215,6 +15377,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-31779.256552160365</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-97996.430158915711</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15234,8 +15399,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="426349696"/>
-        <c:axId val="426347904"/>
+        <c:axId val="502160000"/>
+        <c:axId val="502158464"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -15260,7 +15425,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15440,6 +15605,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15449,7 +15617,7 @@
               <c:f>'model2(2)vol&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -15629,6 +15797,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15650,11 +15821,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="426344832"/>
-        <c:axId val="426346368"/>
+        <c:axId val="502138752"/>
+        <c:axId val="502140288"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="426344832"/>
+        <c:axId val="502138752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15697,14 +15868,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426346368"/>
+        <c:crossAx val="502140288"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="426346368"/>
+        <c:axId val="502140288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15755,12 +15926,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426344832"/>
+        <c:crossAx val="502138752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="426347904"/>
+        <c:axId val="502158464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15797,12 +15968,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426349696"/>
+        <c:crossAx val="502160000"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="426349696"/>
+        <c:axId val="502160000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15811,7 +15982,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="426347904"/>
+        <c:crossAx val="502158464"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15961,7 +16132,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16141,6 +16312,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16150,7 +16324,7 @@
               <c:f>'model2(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16329,6 +16503,9 @@
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>1174811.7958955525</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
               </c:numCache>
@@ -16372,7 +16549,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16552,6 +16729,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16561,7 +16741,7 @@
               <c:f>'model2(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16741,6 +16921,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>2010615.8177554612</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2054661.8557303001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16783,7 +16966,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16963,6 +17146,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16972,7 +17158,7 @@
               <c:f>'model2(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17152,6 +17338,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>835804.02185990871</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>879850.05983474758</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17173,11 +17362,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="440316288"/>
-        <c:axId val="440317824"/>
+        <c:axId val="502286208"/>
+        <c:axId val="502287744"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="440316288"/>
+        <c:axId val="502286208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17220,14 +17409,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="440317824"/>
+        <c:crossAx val="502287744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="440317824"/>
+        <c:axId val="502287744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17278,7 +17467,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="440316288"/>
+        <c:crossAx val="502286208"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17379,7 +17568,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17417,7 +17606,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17460,7 +17649,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17498,7 +17687,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17541,7 +17730,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17579,7 +17768,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17622,7 +17811,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17660,7 +17849,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17703,7 +17892,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17741,7 +17930,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17784,7 +17973,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17822,7 +18011,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17865,7 +18054,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17903,7 +18092,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18214,7 +18403,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -20857,6 +21046,44 @@
         <v>241671.12627942342</v>
       </c>
     </row>
+    <row r="63" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="32">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="31">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="29">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="29">
+        <v>-60139.263576626639</v>
+      </c>
+      <c r="F63" s="30">
+        <v>-47131.083462289775</v>
+      </c>
+      <c r="G63" s="30">
+        <v>1348192.6340495073</v>
+      </c>
+      <c r="H63" s="30">
+        <v>1720293.8319048518</v>
+      </c>
+      <c r="I63" s="30">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J63" s="30">
+        <v>2022104.2217609019</v>
+      </c>
+      <c r="K63" s="30">
+        <v>863611.19227867806</v>
+      </c>
+      <c r="L63" s="29">
+        <v>301810.38985605008</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -20873,7 +21100,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH62"/>
+  <dimension ref="A1:AH63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24217,6 +24444,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="63" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="17">
+        <v>-60139.263576626639</v>
+      </c>
+      <c r="F63" s="18">
+        <v>-47131.083462289775</v>
+      </c>
+      <c r="G63" s="18">
+        <v>1651141.3025257313</v>
+      </c>
+      <c r="H63" s="18">
+        <v>2106856.3398144585</v>
+      </c>
+      <c r="I63" s="18">
+        <v>1319891.5920995933</v>
+      </c>
+      <c r="J63" s="18">
+        <v>2300222.1250249241</v>
+      </c>
+      <c r="K63" s="18">
+        <v>980330.5329253308</v>
+      </c>
+      <c r="L63" s="17">
+        <v>193365.78521046543</v>
+      </c>
+      <c r="M63" s="22">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="N63" s="22">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="O63" s="22">
+        <v>86.230028778736084</v>
+      </c>
+      <c r="P63" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -24233,7 +24510,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH62"/>
+  <dimension ref="A1:AH63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -27577,6 +27854,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="63" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="17">
+        <v>-915628.10722505616</v>
+      </c>
+      <c r="F63" s="18">
+        <v>-717576.87366851489</v>
+      </c>
+      <c r="G63" s="18">
+        <v>13842794.925130703</v>
+      </c>
+      <c r="H63" s="18">
+        <v>17663406.641303208</v>
+      </c>
+      <c r="I63" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J63" s="18">
+        <v>19503027.168851279</v>
+      </c>
+      <c r="K63" s="18">
+        <v>8615191.3953703009</v>
+      </c>
+      <c r="L63" s="17">
+        <v>1839620.5275480719</v>
+      </c>
+      <c r="M63" s="22">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="N63" s="22">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="O63" s="22">
+        <v>86.230028778736084</v>
+      </c>
+      <c r="P63" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -27593,7 +27920,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ62"/>
+  <dimension ref="A1:AJ63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -31309,6 +31636,62 @@
         <v>1</v>
       </c>
     </row>
+    <row r="63" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="17">
+        <v>3094800</v>
+      </c>
+      <c r="F63" s="17">
+        <v>4026308.4497372219</v>
+      </c>
+      <c r="G63" s="17">
+        <v>-97996.430158915711</v>
+      </c>
+      <c r="H63" s="18">
+        <v>-76799.708778299275</v>
+      </c>
+      <c r="I63" s="18">
+        <v>1883423.5569906416</v>
+      </c>
+      <c r="J63" s="18">
+        <v>2403248.501828203</v>
+      </c>
+      <c r="K63" s="18">
+        <v>1319095.5916679052</v>
+      </c>
+      <c r="L63" s="18">
+        <v>2579594.8543026936</v>
+      </c>
+      <c r="M63" s="18">
+        <v>1260499.2626347884</v>
+      </c>
+      <c r="N63" s="17">
+        <v>176346.35247449053</v>
+      </c>
+      <c r="O63" s="22">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="P63" s="22">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="Q63" s="22">
+        <v>86.230028778736084</v>
+      </c>
+      <c r="R63" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J2">
@@ -31325,7 +31708,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ62"/>
+  <dimension ref="A1:AJ63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -34868,6 +35251,59 @@
         <v>1</v>
       </c>
     </row>
+    <row r="63" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="17">
+        <v>-60139.263576626639</v>
+      </c>
+      <c r="F63" s="18">
+        <v>-47131.083462289775</v>
+      </c>
+      <c r="G63" s="18">
+        <v>1373708.0207151792</v>
+      </c>
+      <c r="H63" s="18">
+        <v>1752851.46587425</v>
+      </c>
+      <c r="I63" s="18">
+        <v>1174811.7958955525</v>
+      </c>
+      <c r="J63" s="18">
+        <v>2054661.8557303001</v>
+      </c>
+      <c r="K63" s="18">
+        <v>879850.05983474758</v>
+      </c>
+      <c r="L63" s="17">
+        <v>301810.38985605008</v>
+      </c>
+      <c r="M63" s="21">
+        <v>93.931398043426469</v>
+      </c>
+      <c r="N63" s="21">
+        <v>87.037193073217864</v>
+      </c>
+      <c r="O63" s="21">
+        <v>83.098819498850574</v>
+      </c>
+      <c r="P63" s="21">
+        <v>94.913940221952458</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -34884,7 +35320,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ62"/>
+  <dimension ref="A1:AJ63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -37896,6 +38332,50 @@
         <v>907397.80051921715</v>
       </c>
     </row>
+    <row r="63" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="17">
+        <v>3094800</v>
+      </c>
+      <c r="F63" s="17">
+        <v>4026308.4497372219</v>
+      </c>
+      <c r="G63" s="17">
+        <v>-703792.54386857653</v>
+      </c>
+      <c r="H63" s="18">
+        <v>-551561.54486233124</v>
+      </c>
+      <c r="I63" s="18">
+        <v>11413043.535623506</v>
+      </c>
+      <c r="J63" s="18">
+        <v>14563043.812679429</v>
+      </c>
+      <c r="K63" s="18">
+        <v>8275639.9932962749</v>
+      </c>
+      <c r="L63" s="18">
+        <v>16174234.157067223</v>
+      </c>
+      <c r="M63" s="18">
+        <v>7898594.1637709476</v>
+      </c>
+      <c r="N63" s="17">
+        <v>1611190.3443877937</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J2">
@@ -37912,7 +38392,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -40555,6 +41035,44 @@
         <v>1556201.7813372496</v>
       </c>
     </row>
+    <row r="63" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="31">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="17">
+        <v>-915628.10722505616</v>
+      </c>
+      <c r="F63" s="18">
+        <v>-717576.87366851489</v>
+      </c>
+      <c r="G63" s="18">
+        <v>11261973.499519134</v>
+      </c>
+      <c r="H63" s="18">
+        <v>14370278.443152532</v>
+      </c>
+      <c r="I63" s="18">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J63" s="18">
+        <v>16842108.331714839</v>
+      </c>
+      <c r="K63" s="18">
+        <v>7480773.5139874145</v>
+      </c>
+      <c r="L63" s="17">
+        <v>2471829.8885623058</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ).xlsx
@@ -587,7 +587,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -773,6 +773,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -782,7 +785,7 @@
               <c:f>'model2(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -967,6 +970,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -1010,7 +1016,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1196,6 +1202,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1205,7 +1214,7 @@
               <c:f>'model2(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1391,6 +1400,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1794259.6267486978</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1803474.034715408</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1433,7 +1445,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1619,6 +1631,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1628,7 +1643,7 @@
               <c:f>'model2(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1814,6 +1829,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>635766.59726647404</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>644981.0052331842</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1835,11 +1853,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="90121728"/>
-        <c:axId val="90123264"/>
+        <c:axId val="489281024"/>
+        <c:axId val="489282560"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="90121728"/>
+        <c:axId val="489281024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1882,14 +1900,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90123264"/>
+        <c:crossAx val="489282560"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="90123264"/>
+        <c:axId val="489282560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1940,7 +1958,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90121728"/>
+        <c:crossAx val="489281024"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2101,7 +2119,7 @@
               <c:f>'model2(1)&amp;KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2287,6 +2305,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-35250.090060671617</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-34946.17272282279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2306,8 +2327,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="566240384"/>
-        <c:axId val="566238592"/>
+        <c:axId val="444347520"/>
+        <c:axId val="444341632"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2332,7 +2353,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2518,6 +2539,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2527,7 +2551,7 @@
               <c:f>'model2(1)&amp;KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2713,6 +2737,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2734,11 +2761,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="566235520"/>
-        <c:axId val="566237056"/>
+        <c:axId val="444338560"/>
+        <c:axId val="444340096"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="566235520"/>
+        <c:axId val="444338560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2781,14 +2808,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566237056"/>
+        <c:crossAx val="444340096"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="566237056"/>
+        <c:axId val="444340096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2839,12 +2866,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566235520"/>
+        <c:crossAx val="444338560"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="566238592"/>
+        <c:axId val="444341632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2881,12 +2908,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566240384"/>
+        <c:crossAx val="444347520"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="566240384"/>
+        <c:axId val="444347520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2895,7 +2922,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="566238592"/>
+        <c:crossAx val="444341632"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3045,7 +3072,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3231,6 +3258,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3240,7 +3270,7 @@
               <c:f>'model2(2)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3425,6 +3455,9 @@
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>8275639.9932962749</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
               </c:numCache>
@@ -3468,7 +3501,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3654,6 +3687,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3663,7 +3699,7 @@
               <c:f>'model2(2)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3849,6 +3885,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>14245429.46213273</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>14323097.271860281</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3891,7 +3930,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4077,6 +4116,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4086,7 +4128,7 @@
               <c:f>'model2(2)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4272,6 +4314,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>5969789.4688364547</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6047457.2785640061</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4293,11 +4338,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="566296960"/>
-        <c:axId val="566298496"/>
+        <c:axId val="444395904"/>
+        <c:axId val="444397440"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="566296960"/>
+        <c:axId val="444395904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4340,14 +4385,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566298496"/>
+        <c:crossAx val="444397440"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="566298496"/>
+        <c:axId val="444397440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4398,7 +4443,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566296960"/>
+        <c:crossAx val="444395904"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4559,7 +4604,7 @@
               <c:f>'model2(2)vol'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4745,6 +4790,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-351576.30531150417</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-130359.36832865544</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4764,8 +4812,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="566351360"/>
-        <c:axId val="566349824"/>
+        <c:axId val="444564992"/>
+        <c:axId val="444563456"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4790,7 +4838,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4976,6 +5024,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4985,7 +5036,7 @@
               <c:f>'model2(2)vol'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5171,6 +5222,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5192,11 +5246,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="566342400"/>
-        <c:axId val="566343936"/>
+        <c:axId val="444560128"/>
+        <c:axId val="444561664"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="566342400"/>
+        <c:axId val="444560128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5239,14 +5293,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566343936"/>
+        <c:crossAx val="444561664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="566343936"/>
+        <c:axId val="444561664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5297,12 +5351,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566342400"/>
+        <c:crossAx val="444560128"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="566349824"/>
+        <c:axId val="444563456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5339,12 +5393,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566351360"/>
+        <c:crossAx val="444564992"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="566351360"/>
+        <c:axId val="444564992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5353,7 +5407,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="566349824"/>
+        <c:crossAx val="444563456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5503,7 +5557,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5689,6 +5743,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5698,7 +5755,7 @@
               <c:f>'model2(2)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5883,6 +5940,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -5926,7 +5986,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6112,6 +6172,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6121,7 +6184,7 @@
               <c:f>'model2(2)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6307,6 +6370,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>14938834.477348203</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>15015678.778184865</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6349,7 +6415,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6535,6 +6601,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6544,7 +6613,7 @@
               <c:f>'model2(2)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6730,6 +6799,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>5577499.6596207786</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5654343.9604574405</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6751,11 +6823,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="566465280"/>
-        <c:axId val="566466816"/>
+        <c:axId val="444666624"/>
+        <c:axId val="444668160"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="566465280"/>
+        <c:axId val="444666624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6798,14 +6870,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566466816"/>
+        <c:crossAx val="444668160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="566466816"/>
+        <c:axId val="444668160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6856,7 +6928,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566465280"/>
+        <c:crossAx val="444666624"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7017,7 +7089,7 @@
               <c:f>'model2(2)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7203,6 +7275,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-314574.39222416701</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-309173.41467680095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7222,8 +7297,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="567084928"/>
-        <c:axId val="567083392"/>
+        <c:axId val="444737408"/>
+        <c:axId val="444735872"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7248,7 +7323,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7434,6 +7509,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7443,7 +7521,7 @@
               <c:f>'model2(2)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7629,6 +7707,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7650,11 +7731,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="566486144"/>
-        <c:axId val="566487680"/>
+        <c:axId val="444732544"/>
+        <c:axId val="444734080"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="566486144"/>
+        <c:axId val="444732544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7697,14 +7778,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566487680"/>
+        <c:crossAx val="444734080"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="566487680"/>
+        <c:axId val="444734080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7755,12 +7836,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566486144"/>
+        <c:crossAx val="444732544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="567083392"/>
+        <c:axId val="444735872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7797,12 +7878,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="567084928"/>
+        <c:crossAx val="444737408"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="567084928"/>
+        <c:axId val="444737408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7811,7 +7892,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="567083392"/>
+        <c:crossAx val="444735872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7943,7 +8024,7 @@
               <c:f>'model2(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8129,6 +8210,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-35250.090060671617</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-34946.17272282279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8148,8 +8232,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="90163840"/>
-        <c:axId val="90162304"/>
+        <c:axId val="392784512"/>
+        <c:axId val="392782976"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8174,7 +8258,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8360,6 +8444,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8369,7 +8456,7 @@
               <c:f>'model2(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8555,6 +8642,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8576,11 +8666,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="90158976"/>
-        <c:axId val="90160512"/>
+        <c:axId val="526648832"/>
+        <c:axId val="526650752"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="90158976"/>
+        <c:axId val="526648832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8623,14 +8713,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90160512"/>
+        <c:crossAx val="526650752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="90160512"/>
+        <c:axId val="526650752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8681,12 +8771,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90158976"/>
+        <c:crossAx val="526648832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="90162304"/>
+        <c:axId val="392782976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8723,12 +8813,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90163840"/>
+        <c:crossAx val="392784512"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="90163840"/>
+        <c:axId val="392784512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8737,7 +8827,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="90162304"/>
+        <c:crossAx val="392782976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8887,7 +8977,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9073,6 +9163,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9082,7 +9175,7 @@
               <c:f>'model2(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9267,6 +9360,9 @@
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>1319891.5920995933</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
               </c:numCache>
@@ -9310,7 +9406,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9496,6 +9592,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9505,7 +9604,7 @@
               <c:f>'model2(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9691,6 +9790,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>2021179.1960838926</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2032514.2354846764</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9733,7 +9835,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9919,6 +10021,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9928,7 +10033,7 @@
               <c:f>'model2(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10114,6 +10219,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>701287.60398429935</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>712622.64338508318</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10135,11 +10243,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="90261376"/>
-        <c:axId val="90262912"/>
+        <c:axId val="427054976"/>
+        <c:axId val="427056512"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="90261376"/>
+        <c:axId val="427054976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10182,14 +10290,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90262912"/>
+        <c:crossAx val="427056512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="90262912"/>
+        <c:axId val="427056512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10240,7 +10348,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90261376"/>
+        <c:crossAx val="427054976"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10422,7 +10530,7 @@
               <c:f>'model2(1)&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10608,6 +10716,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-35250.090060671617</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-6989.2345445645587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10627,8 +10738,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="90299776"/>
-        <c:axId val="90298240"/>
+        <c:axId val="428780928"/>
+        <c:axId val="428779392"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10653,7 +10764,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10839,6 +10950,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10848,7 +10962,7 @@
               <c:f>'model2(1)&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -11034,6 +11148,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11055,11 +11172,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="90286720"/>
-        <c:axId val="90296704"/>
+        <c:axId val="428747392"/>
+        <c:axId val="428777856"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="90286720"/>
+        <c:axId val="428747392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11102,14 +11219,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90296704"/>
+        <c:crossAx val="428777856"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="90296704"/>
+        <c:axId val="428777856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11160,12 +11277,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90286720"/>
+        <c:crossAx val="428747392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="90298240"/>
+        <c:axId val="428779392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11202,12 +11319,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90299776"/>
+        <c:crossAx val="428780928"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="90299776"/>
+        <c:axId val="428780928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11216,7 +11333,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="90298240"/>
+        <c:crossAx val="428779392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11366,7 +11483,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11552,6 +11669,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11561,7 +11681,7 @@
               <c:f>'model2(2)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11746,6 +11866,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -11789,7 +11912,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11975,6 +12098,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11984,7 +12110,7 @@
               <c:f>'model2(2)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12170,6 +12296,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>17163594.417257134</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>17258504.389312655</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12212,7 +12341,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12398,6 +12527,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12407,7 +12539,7 @@
               <c:f>'model2(2)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12593,6 +12725,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>6275758.643776156</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6370668.6158316769</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12614,11 +12749,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="103930496"/>
-        <c:axId val="166998400"/>
+        <c:axId val="429042304"/>
+        <c:axId val="429056384"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="103930496"/>
+        <c:axId val="429042304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12661,14 +12796,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="166998400"/>
+        <c:crossAx val="429056384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="166998400"/>
+        <c:axId val="429056384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12719,7 +12854,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="103930496"/>
+        <c:crossAx val="429042304"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12901,7 +13036,7 @@
               <c:f>'model2(2)&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13087,6 +13222,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-314574.39222416701</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-61834.682935360193</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13106,8 +13244,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="167027456"/>
-        <c:axId val="167025664"/>
+        <c:axId val="429093632"/>
+        <c:axId val="429079552"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -13132,7 +13270,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13318,6 +13456,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13327,7 +13468,7 @@
               <c:f>'model2(2)&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -13513,6 +13654,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13534,11 +13678,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="167022592"/>
-        <c:axId val="167024128"/>
+        <c:axId val="429076480"/>
+        <c:axId val="429078016"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="167022592"/>
+        <c:axId val="429076480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13581,14 +13725,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="167024128"/>
+        <c:crossAx val="429078016"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="167024128"/>
+        <c:axId val="429078016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13639,12 +13783,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="167022592"/>
+        <c:crossAx val="429076480"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="167025664"/>
+        <c:axId val="429079552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13681,12 +13825,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="167027456"/>
+        <c:crossAx val="429093632"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="167027456"/>
+        <c:axId val="429093632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13695,7 +13839,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="167025664"/>
+        <c:crossAx val="429079552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13845,7 +13989,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14031,6 +14175,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14040,7 +14187,7 @@
               <c:f>'model2(2)vol&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14225,6 +14372,9 @@
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>1319095.5916679052</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
               </c:numCache>
@@ -14268,7 +14418,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14454,6 +14604,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14463,7 +14616,7 @@
               <c:f>'model2(2)vol&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14649,6 +14802,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>2261296.217489922</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2274170.572835926</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14691,7 +14847,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14877,6 +15033,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14886,7 +15045,7 @@
               <c:f>'model2(2)vol&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15072,6 +15231,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>942200.62582201674</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>955074.98116802075</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15093,11 +15255,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="373633024"/>
-        <c:axId val="373634560"/>
+        <c:axId val="429211648"/>
+        <c:axId val="429213184"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="373633024"/>
+        <c:axId val="429211648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15140,14 +15302,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="373634560"/>
+        <c:crossAx val="429213184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="373634560"/>
+        <c:axId val="429213184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15198,7 +15360,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="373633024"/>
+        <c:crossAx val="429211648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15359,7 +15521,7 @@
               <c:f>'model2(2)vol&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15545,6 +15707,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-48953.662764892986</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-3630.2608901650879</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15564,8 +15729,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="412185344"/>
-        <c:axId val="412183552"/>
+        <c:axId val="430417024"/>
+        <c:axId val="430415232"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -15590,7 +15755,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15776,6 +15941,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15785,7 +15953,7 @@
               <c:f>'model2(2)vol&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -15971,6 +16139,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15992,11 +16163,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="412180480"/>
-        <c:axId val="412182016"/>
+        <c:axId val="430412160"/>
+        <c:axId val="430413696"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="412180480"/>
+        <c:axId val="430412160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16039,14 +16210,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="412182016"/>
+        <c:crossAx val="430413696"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="412182016"/>
+        <c:axId val="430413696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16097,12 +16268,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="412180480"/>
+        <c:crossAx val="430412160"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="412183552"/>
+        <c:axId val="430415232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16139,12 +16310,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="412185344"/>
+        <c:crossAx val="430417024"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="412185344"/>
+        <c:axId val="430417024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16153,7 +16324,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="412183552"/>
+        <c:crossAx val="430415232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16303,7 +16474,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16489,6 +16660,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16498,7 +16672,7 @@
               <c:f>'model2(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16683,6 +16857,9 @@
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>1174811.7958955525</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
               </c:numCache>
@@ -16726,7 +16903,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16912,6 +17089,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16921,7 +17101,7 @@
               <c:f>'model2(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17107,6 +17287,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1822505.1596172629</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1831898.1745119649</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17149,7 +17332,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -17335,6 +17518,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17344,7 +17530,7 @@
               <c:f>'model2(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17530,6 +17716,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>647693.3637217104</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>657086.3786164124</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17551,11 +17740,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="491237376"/>
-        <c:axId val="491238912"/>
+        <c:axId val="430489600"/>
+        <c:axId val="430491136"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="491237376"/>
+        <c:axId val="430489600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17598,14 +17787,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="491238912"/>
+        <c:crossAx val="430491136"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="491238912"/>
+        <c:axId val="430491136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17656,7 +17845,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="491237376"/>
+        <c:crossAx val="430489600"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -18592,7 +18781,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -21311,6 +21500,44 @@
         <v>337060.4799167217</v>
       </c>
     </row>
+    <row r="65" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="32">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="31">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="29">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="29">
+        <v>-34946.17272282279</v>
+      </c>
+      <c r="F65" s="30">
+        <v>-31369.994514880033</v>
+      </c>
+      <c r="G65" s="30">
+        <v>1284979.7395587955</v>
+      </c>
+      <c r="H65" s="30">
+        <v>1431467.3820758634</v>
+      </c>
+      <c r="I65" s="30">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J65" s="30">
+        <v>1803474.034715408</v>
+      </c>
+      <c r="K65" s="30">
+        <v>644981.0052331842</v>
+      </c>
+      <c r="L65" s="29">
+        <v>372006.65263954451</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -21327,7 +21554,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH64"/>
+  <dimension ref="A1:AH65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24771,6 +24998,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="17">
+        <v>-6989.2345445645587</v>
+      </c>
+      <c r="F65" s="18">
+        <v>-6273.9989029760072</v>
+      </c>
+      <c r="G65" s="18">
+        <v>1613024.4036469234</v>
+      </c>
+      <c r="H65" s="18">
+        <v>1796909.1256689748</v>
+      </c>
+      <c r="I65" s="18">
+        <v>1319891.5920995933</v>
+      </c>
+      <c r="J65" s="18">
+        <v>2032514.2354846764</v>
+      </c>
+      <c r="K65" s="18">
+        <v>712622.64338508318</v>
+      </c>
+      <c r="L65" s="17">
+        <v>235605.10981570161</v>
+      </c>
+      <c r="M65" s="22">
+        <v>2.9890860469234198E-2</v>
+      </c>
+      <c r="N65" s="22">
+        <v>5.7377062222749194E-2</v>
+      </c>
+      <c r="O65" s="22">
+        <v>52.095487833085492</v>
+      </c>
+      <c r="P65" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -24787,7 +25064,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH64"/>
+  <dimension ref="A1:AH65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -28231,6 +28508,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="17">
+        <v>-61834.682935360193</v>
+      </c>
+      <c r="F65" s="18">
+        <v>-55506.898563595001</v>
+      </c>
+      <c r="G65" s="18">
+        <v>13503119.648860516</v>
+      </c>
+      <c r="H65" s="18">
+        <v>15042474.786605056</v>
+      </c>
+      <c r="I65" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J65" s="18">
+        <v>17258504.389312655</v>
+      </c>
+      <c r="K65" s="18">
+        <v>6370668.6158316769</v>
+      </c>
+      <c r="L65" s="17">
+        <v>2216029.6027075993</v>
+      </c>
+      <c r="M65" s="22">
+        <v>2.9890860469234198E-2</v>
+      </c>
+      <c r="N65" s="22">
+        <v>5.7377062222749194E-2</v>
+      </c>
+      <c r="O65" s="22">
+        <v>52.095487833085492</v>
+      </c>
+      <c r="P65" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -28247,7 +28574,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ64"/>
+  <dimension ref="A1:AJ65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -32075,6 +32402,62 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="17">
+        <v>1687200</v>
+      </c>
+      <c r="F65" s="17">
+        <v>4001533.5447742641</v>
+      </c>
+      <c r="G65" s="17">
+        <v>-3630.2608901650879</v>
+      </c>
+      <c r="H65" s="18">
+        <v>-3258.762128697666</v>
+      </c>
+      <c r="I65" s="18">
+        <v>1835942.877011803</v>
+      </c>
+      <c r="J65" s="18">
+        <v>2045240.2967063773</v>
+      </c>
+      <c r="K65" s="18">
+        <v>1319095.5916679052</v>
+      </c>
+      <c r="L65" s="18">
+        <v>2274170.572835926</v>
+      </c>
+      <c r="M65" s="18">
+        <v>955074.98116802075</v>
+      </c>
+      <c r="N65" s="17">
+        <v>228930.27612954858</v>
+      </c>
+      <c r="O65" s="22">
+        <v>2.9890860469234198E-2</v>
+      </c>
+      <c r="P65" s="22">
+        <v>5.7377062222749194E-2</v>
+      </c>
+      <c r="Q65" s="22">
+        <v>52.095487833085492</v>
+      </c>
+      <c r="R65" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J2">
@@ -32091,7 +32474,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ64"/>
+  <dimension ref="A1:AJ65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -35740,6 +36123,59 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="17">
+        <v>-34946.17272282279</v>
+      </c>
+      <c r="F65" s="18">
+        <v>-31369.994514880033</v>
+      </c>
+      <c r="G65" s="18">
+        <v>1310495.1262244673</v>
+      </c>
+      <c r="H65" s="18">
+        <v>1459891.5218724203</v>
+      </c>
+      <c r="I65" s="18">
+        <v>1174811.7958955525</v>
+      </c>
+      <c r="J65" s="18">
+        <v>1831898.1745119649</v>
+      </c>
+      <c r="K65" s="18">
+        <v>657086.3786164124</v>
+      </c>
+      <c r="L65" s="17">
+        <v>372006.65263954451</v>
+      </c>
+      <c r="M65" s="21">
+        <v>31.202982920806502</v>
+      </c>
+      <c r="N65" s="21">
+        <v>57.963077631244182</v>
+      </c>
+      <c r="O65" s="21">
+        <v>72.982292563465052</v>
+      </c>
+      <c r="P65" s="21">
+        <v>27.924647766802451</v>
+      </c>
+      <c r="Q65" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -35756,7 +36192,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ64"/>
+  <dimension ref="A1:AJ65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -38856,6 +39292,50 @@
         <v>1962766.6496992977</v>
       </c>
     </row>
+    <row r="65" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="17">
+        <v>1687200</v>
+      </c>
+      <c r="F65" s="17">
+        <v>4001533.5447742641</v>
+      </c>
+      <c r="G65" s="17">
+        <v>-130359.36832865544</v>
+      </c>
+      <c r="H65" s="18">
+        <v>-117019.18553050711</v>
+      </c>
+      <c r="I65" s="18">
+        <v>10978430.576441985</v>
+      </c>
+      <c r="J65" s="18">
+        <v>12229971.253832327</v>
+      </c>
+      <c r="K65" s="18">
+        <v>8275639.9932962749</v>
+      </c>
+      <c r="L65" s="18">
+        <v>14323097.271860281</v>
+      </c>
+      <c r="M65" s="18">
+        <v>6047457.2785640061</v>
+      </c>
+      <c r="N65" s="17">
+        <v>2093126.0180279531</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J2">
@@ -38872,7 +39352,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -41591,6 +42071,44 @@
         <v>2786404.2807864728</v>
       </c>
     </row>
+    <row r="65" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="31">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="17">
+        <v>-309173.41467680095</v>
+      </c>
+      <c r="F65" s="18">
+        <v>-277534.492817975</v>
+      </c>
+      <c r="G65" s="18">
+        <v>10700270.628994567</v>
+      </c>
+      <c r="H65" s="18">
+        <v>11920101.082721591</v>
+      </c>
+      <c r="I65" s="18">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J65" s="18">
+        <v>15015678.778184865</v>
+      </c>
+      <c r="K65" s="18">
+        <v>5654343.9604574405</v>
+      </c>
+      <c r="L65" s="17">
+        <v>3095577.6954632737</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
